--- a/data/trans_orig/IP1010-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP1010-Estudios-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>3229</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4080</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>636</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5373</t>
+          <t>5305</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87362</t>
+          <t>87638</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>82765</t>
+          <t>82716</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>172339</t>
+          <t>172407</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>177073</t>
+          <t>177076</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5394</t>
+          <t>5637</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>727</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6161</t>
+          <t>6235</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>413045</t>
+          <t>413043</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>471597</t>
+          <t>471354</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>886917</t>
+          <t>886843</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>892410</t>
+          <t>892351</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>99,92%</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4194</t>
+          <t>3834</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4467</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>153944</t>
+          <t>154304</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>327738</t>
+          <t>328264</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4323</t>
+          <t>4360</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9234</t>
+          <t>9275</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>2772</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11162</t>
+          <t>11200</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>676698</t>
+          <t>676661</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>712740</t>
+          <t>712699</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>720021</t>
+          <t>720008</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1391833</t>
+          <t>1391795</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1399895</t>
+          <t>1400223</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3518</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3421</t>
+          <t>3641</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>80019</t>
+          <t>80418</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>172004</t>
+          <t>171784</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6057</t>
+          <t>5774</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>646</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5385</t>
+          <t>5419</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8098</t>
+          <t>8646</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>443643</t>
+          <t>443926</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>487019</t>
+          <t>486985</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>491757</t>
+          <t>491758</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>934005</t>
+          <t>933457</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>940761</t>
+          <t>940702</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,85%</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2213</t>
+          <t>2537</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2259</t>
+          <t>2511</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>163127</t>
+          <t>162803</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>334642</t>
+          <t>334390</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>443</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5962</t>
+          <t>6428</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>689</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6611</t>
+          <t>6724</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>2072</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9506</t>
+          <t>9577</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>700966</t>
+          <t>700500</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>706928</t>
+          <t>706485</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>740890</t>
+          <t>740777</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>746856</t>
+          <t>746812</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1444923</t>
+          <t>1444852</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1452381</t>
+          <t>1452357</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1437</t>
+          <t>1452</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8495</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2083</t>
+          <t>1908</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10127</t>
+          <t>9444</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>469648</t>
+          <t>469650</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>480240</t>
+          <t>480231</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>487298</t>
+          <t>487283</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>950898</t>
+          <t>951581</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>958942</t>
+          <t>959117</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4664,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4388</t>
+          <t>4076</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4107</t>
+          <t>4050</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>183107</t>
+          <t>183419</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>356090</t>
+          <t>356147</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2983</t>
+          <t>2598</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2171</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10137</t>
+          <t>10557</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2643</t>
+          <t>2558</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10800</t>
+          <t>10088</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -5080,7 +5080,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>701388</t>
+          <t>701773</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>734707</t>
+          <t>734287</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>742665</t>
+          <t>742673</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1438415</t>
+          <t>1439127</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1446572</t>
+          <t>1446657</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">

--- a/data/trans_orig/IP1010-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP1010-Estudios-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1343</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4710</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5,42%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>642</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3229</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3901</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,71%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1343</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4129</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>637</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5305</t>
+          <t>5346</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>85502</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>82135</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,45%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>94,58%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>90225</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>87638</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>86966</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,29%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>96,45%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,71%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>85502</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>82716</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,45%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>95,25%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>263</t>
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>172407</t>
+          <t>172366</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>177076</t>
+          <t>177075</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,74 +1065,74 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6036</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>605</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3044</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3038</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,15%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>0,73%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2040</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5637</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>4</t>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>645</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6235</t>
+          <t>6152</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>716</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>474951</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>470955</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>476344</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,57%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,73%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,86%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>627</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>415482</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>413043</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>413049</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,85%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>99,27%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>716</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>474951</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>471354</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>476344</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,57%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,82%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,86%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1343</t>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>886843</t>
+          <t>886926</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>892351</t>
+          <t>892433</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,93%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,107 +1408,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1275</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4533</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>1275</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3834</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4002</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1275</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3941</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>156863</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>153605</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,19%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,13%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>156863</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>154304</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,19%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>97,58%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>488</t>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>328264</t>
+          <t>328203</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,74 +1751,74 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4658</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1951</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9248</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1247</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4360</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4377</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,18%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>0,64%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4658</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1966</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9275</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>9</t>
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2772</t>
+          <t>2712</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11200</t>
+          <t>10771</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1078</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>717316</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>712726</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>720023</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,35%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,72%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>679774</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>676661</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>676644</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,82%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>99,36%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1078</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>717316</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>712699</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>720008</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,35%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,72%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2094</t>
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1391795</t>
+          <t>1392224</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1400223</t>
+          <t>1400283</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,81%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1085</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2157,7 +2157,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2325,107 +2325,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3110</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,72%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>624</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3119</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4242</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>3,73%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>624</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3641</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -2438,74 +2438,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>82913</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>80427</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,25%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>96,28%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>82913</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>80418</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>96,27%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>249</t>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>171784</t>
+          <t>171183</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2551,57 +2551,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2668,72 +2668,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5463</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1652</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5774</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5794</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,37%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5419</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8646</t>
+          <t>8324</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -2781,74 +2781,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>490379</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>486941</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>491759</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,59%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,89%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,87%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>649</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>448048</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>443926</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>443906</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>449700</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,63%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,72%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,71%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>702</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>490379</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>486985</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>491758</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,59%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,9%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,87%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1351</t>
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>933457</t>
+          <t>933779</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>940702</t>
+          <t>940728</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -2894,57 +2894,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>651</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3011,107 +3011,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>443</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2537</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2143</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,27%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>2269</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>443</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>2511</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -3124,74 +3124,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>164897</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>162803</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>163197</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,73%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>98,47%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>98,7%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>476</t>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>334390</t>
+          <t>334632</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3237,57 +3237,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3354,72 +3354,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2649</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6367</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2095</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>443</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6428</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7101</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,3%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,06%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>689</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6724</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2072</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9577</t>
+          <t>8839</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -3467,74 +3467,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1061</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>744852</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>741134</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>746851</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,65%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>99,15%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,91%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1015</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>704833</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>700500</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>699827</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>706485</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,7%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>99,09%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>99,0%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,94%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1061</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>744852</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>740777</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>746812</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,65%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,91%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2076</t>
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1444852</t>
+          <t>1445590</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1452357</t>
+          <t>1452426</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3580,57 +3580,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3760,7 +3760,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4041,47 +4041,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4154,57 +4154,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4271,72 +4271,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4239</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1442</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8514</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>524</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2640</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2994</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,11%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4239</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1452</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>8504</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1908</t>
+          <t>1978</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9444</t>
+          <t>9733</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -4384,74 +4384,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>689</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>484496</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>480221</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>487293</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,13%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,26%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,7%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>713</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>471766</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>469650</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>469296</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,89%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>99,44%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>99,37%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>689</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>484496</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>480231</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>487283</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,13%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,26%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,7%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1402</t>
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>951581</t>
+          <t>951292</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>959117</t>
+          <t>959047</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -4497,57 +4497,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>714</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4614,107 +4614,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4092</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,18%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>818</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4076</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4096</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>818</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4050</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -4727,74 +4727,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>186677</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>183403</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,56%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,82%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>186677</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>183419</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>97,83%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>528</t>
@@ -4807,7 +4807,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>356147</t>
+          <t>356101</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4840,57 +4840,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4957,72 +4957,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5057</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2192</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10311</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>524</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2598</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3127</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,07%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>5057</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2171</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>10557</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2558</t>
+          <t>2663</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10088</t>
+          <t>11001</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -5070,74 +5070,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1058</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>739787</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>734533</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>742652</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,32%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,62%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,71%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1060</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>703847</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>701773</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>701244</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,93%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>99,56%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1058</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>739787</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>734287</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>742673</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,32%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,58%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2118</t>
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1439127</t>
+          <t>1438214</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1446657</t>
+          <t>1446552</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5183,57 +5183,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
